--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487896_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487896_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5086</v>
+        <v>8.676299999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0959</v>
+        <v>7.9113</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4127</v>
+        <v>0.765</v>
       </c>
       <c r="G2" t="n">
         <v>7.7493</v>
@@ -610,13 +610,13 @@
         <v>1.2487</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8057</v>
+        <v>0.3619</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.162</v>
+        <v>-0.3467</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3563</v>
+        <v>0.7086</v>
       </c>
       <c r="V2" t="n">
         <v>1.3975</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. STRIKKER</t>
+          <t>A. MAZAIRA GOMEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9671</v>
+        <v>3.4722</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0859</v>
+        <v>2.0332</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8812</v>
+        <v>1.4389</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2983</v>
+        <v>-0.1564</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4992</v>
+        <v>-0.7655</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2008</v>
+        <v>0.609</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6416</v>
+        <v>1.4032</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9933999999999999</v>
+        <v>-0.1284</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6482</v>
+        <v>1.5316</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3433</v>
+        <v>-1.5596</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4942</v>
+        <v>-0.6371</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8491</v>
+        <v>-0.9225</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4162</v>
+        <v>1.8731</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6244</v>
+        <v>1.8731</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3951</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>1.565</v>
+        <v>0.0463</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8301</v>
+        <v>0.6479</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6899</v>
+        <v>1.0614</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.5838</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.23</v>
+        <v>0.4776</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MAZAIRA GOMEZ</t>
+          <t>M. STRIKKER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3324</v>
+        <v>2.4808</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5394</v>
+        <v>2.1867</v>
       </c>
       <c r="F4" t="n">
-        <v>0.793</v>
+        <v>0.294</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1564</v>
+        <v>0.2983</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7655</v>
+        <v>0.4992</v>
       </c>
       <c r="I4" t="n">
-        <v>0.609</v>
+        <v>-0.2008</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4032</v>
+        <v>1.6416</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1284</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5316</v>
+        <v>0.6482</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5596</v>
+        <v>-1.3433</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6371</v>
+        <v>-0.4942</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9225</v>
+        <v>-0.8491</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8731</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8731</v>
+        <v>0.6244</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4456</v>
+        <v>1.9088</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4476</v>
+        <v>0.6659</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002</v>
+        <v>1.2429</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0614</v>
+        <v>0.6899</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5838</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4776</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W. LEVEQUE</t>
+          <t>P. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2532</v>
+        <v>2.0557</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7112000000000001</v>
+        <v>1.569</v>
       </c>
       <c r="F5" t="n">
-        <v>1.542</v>
+        <v>0.4867</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3337</v>
+        <v>0.3717</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006</v>
+        <v>3.0683</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3396</v>
+        <v>-2.6966</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2586</v>
+        <v>1.3148</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3573</v>
+        <v>2.8399</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9013</v>
+        <v>-1.5251</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5923</v>
+        <v>-0.9431</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3513</v>
+        <v>0.2284</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2409</v>
+        <v>-1.1716</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.8325</v>
+        <v>1.6649</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2487</v>
+        <v>1.6649</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4818</v>
+        <v>-0.3347</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1363</v>
+        <v>-0.3295</v>
       </c>
       <c r="U5" t="n">
-        <v>2.3455</v>
+        <v>-0.0052</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9376</v>
+        <v>0.3538</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3975</v>
+        <v>0.5838</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4599</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. CAMPENY LLOVERAS</t>
+          <t>W. LEVEQUE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7197</v>
+        <v>1.3115</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4385</v>
+        <v>0.5621</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2812</v>
+        <v>0.7493</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3717</v>
+        <v>-0.3337</v>
       </c>
       <c r="H6" t="n">
-        <v>3.0683</v>
+        <v>0.006</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.6966</v>
+        <v>-0.3396</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3148</v>
+        <v>1.2586</v>
       </c>
       <c r="K6" t="n">
-        <v>2.8399</v>
+        <v>0.3573</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.5251</v>
+        <v>0.9013</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9431</v>
+        <v>-1.5923</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2284</v>
+        <v>-0.3513</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1716</v>
+        <v>-1.2409</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6649</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6649</v>
+        <v>1.2487</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6707</v>
+        <v>1.54</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.46</v>
+        <v>-0.0128</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2107</v>
+        <v>1.5528</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3538</v>
+        <v>0.9376</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5838</v>
+        <v>1.3975</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.23</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5241</v>
+        <v>0.1166</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6045</v>
+        <v>-1.1106</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0804</v>
+        <v>1.2272</v>
       </c>
       <c r="G7" t="n">
         <v>0.7006</v>
@@ -1000,13 +1000,13 @@
         <v>1.2487</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9550999999999999</v>
+        <v>-0.3144</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8482</v>
+        <v>-0.3543</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.107</v>
+        <v>0.0398</v>
       </c>
       <c r="V7" t="n">
         <v>-0.4776</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7366</v>
+        <v>-0.623</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0069</v>
+        <v>0.1655</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7298</v>
+        <v>-0.7885</v>
       </c>
       <c r="G8" t="n">
         <v>0.1314</v>
@@ -1078,13 +1078,13 @@
         <v>0.8325</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.533</v>
+        <v>-0.4193</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3915</v>
+        <v>-0.2191</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1416</v>
+        <v>-0.2003</v>
       </c>
       <c r="V8" t="n">
         <v>-1.1675</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.1001</v>
+        <v>-3.4404</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.6442</v>
+        <v>-3.0432</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4559</v>
+        <v>-0.3972</v>
       </c>
       <c r="G9" t="n">
         <v>-3.3156</v>
@@ -1156,13 +1156,13 @@
         <v>0.6244</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4952</v>
+        <v>0.1646</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.901</v>
+        <v>-0.3</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4058</v>
+        <v>0.4645</v>
       </c>
       <c r="V9" t="n">
         <v>1.1675</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.7241</v>
+        <v>-8.7011</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.3464</v>
+        <v>-7.3527</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3778</v>
+        <v>-1.3484</v>
       </c>
       <c r="G10" t="n">
         <v>-3.098</v>
@@ -1234,13 +1234,13 @@
         <v>1.0406</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5383</v>
+        <v>0.5614</v>
       </c>
       <c r="T10" t="n">
-        <v>1.295</v>
+        <v>0.2886</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2434</v>
+        <v>0.2727</v>
       </c>
       <c r="V10" t="n">
         <v>-3.0427</v>
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4.696099999999998</v>
+        <v>5.348599999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>2.268900000000001</v>
+        <v>2.9213</v>
       </c>
       <c r="F11" t="n">
         <v>2.427</v>
       </c>
       <c r="G11" t="n">
-        <v>2.3476</v>
+        <v>2.347600000000001</v>
       </c>
       <c r="H11" t="n">
         <v>4.307</v>
@@ -1300,7 +1300,7 @@
         <v>-2.0224</v>
       </c>
       <c r="O11" t="n">
-        <v>-6.735399999999999</v>
+        <v>-6.735399999999998</v>
       </c>
       <c r="P11" t="n">
         <v>-2.0812</v>
@@ -1312,16 +1312,16 @@
         <v>10.406</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5099</v>
+        <v>4.1624</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.214</v>
+        <v>-0.5615999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>4.7238</v>
+        <v>4.7237</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9198999999999993</v>
+        <v>0.9198999999999997</v>
       </c>
       <c r="W11" t="n">
         <v>4.8648</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.2565</v>
+        <v>4.9249</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4097</v>
+        <v>3.0527</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8468</v>
+        <v>1.8722</v>
       </c>
       <c r="G12" t="n">
         <v>3.6239</v>
@@ -1390,13 +1390,13 @@
         <v>1.8731</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6993</v>
+        <v>-0.031</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2148</v>
+        <v>-0.5719</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5155</v>
+        <v>0.5409</v>
       </c>
       <c r="V12" t="n">
         <v>0.7076</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7087</v>
+        <v>3.4904</v>
       </c>
       <c r="E13" t="n">
-        <v>4.0325</v>
+        <v>3.8182</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3238</v>
+        <v>-0.3277</v>
       </c>
       <c r="G13" t="n">
         <v>2.4397</v>
@@ -1468,13 +1468,13 @@
         <v>1.8731</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.396</v>
+        <v>-0.6142</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5657</v>
+        <v>-0.78</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1697</v>
+        <v>0.1658</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>W. NIANG</t>
+          <t>A. RODRIGUEZ MONTON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0876</v>
+        <v>1.5191</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.061</v>
+        <v>0.7905</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1486</v>
+        <v>0.7286</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5868</v>
+        <v>1.9532</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3175</v>
+        <v>0.7294</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7307</v>
+        <v>1.2238</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6196</v>
+        <v>1.3124</v>
       </c>
       <c r="K14" t="n">
-        <v>1.8524</v>
+        <v>0.0192</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.2328</v>
+        <v>1.2932</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0328</v>
+        <v>0.6408</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5349</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5021</v>
+        <v>-0.0694</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.2081</v>
+        <v>0.2081</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.0406</v>
+        <v>0.2081</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0013</v>
+        <v>-0.4123</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4319</v>
+        <v>-0.5219</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4332</v>
+        <v>0.1096</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7076</v>
+        <v>-0.23</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7076</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ MONTON</t>
+          <t>W. NIANG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0532</v>
+        <v>1.0289</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7905</v>
+        <v>-1.061</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2628</v>
+        <v>2.0899</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9532</v>
+        <v>0.5868</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7294</v>
+        <v>1.3175</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2238</v>
+        <v>-0.7307</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3124</v>
+        <v>0.6196</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0192</v>
+        <v>1.8524</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2932</v>
+        <v>-1.2328</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6408</v>
+        <v>-0.0328</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7102000000000001</v>
+        <v>-0.5349</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0694</v>
+        <v>0.5021</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2081</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.2487</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2081</v>
+        <v>1.0406</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8781</v>
+        <v>-0.0574</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5219</v>
+        <v>-0.4319</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3562</v>
+        <v>0.3745</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.23</v>
+        <v>0.7076</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.23</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4251</v>
+        <v>0.0052</v>
       </c>
       <c r="E16" t="n">
-        <v>0.07779999999999999</v>
+        <v>-0.1365</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3473</v>
+        <v>0.1418</v>
       </c>
       <c r="G16" t="n">
         <v>0.9871</v>
@@ -1702,13 +1702,13 @@
         <v>0.6244</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0217</v>
+        <v>0.6018</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2577</v>
+        <v>0.0434</v>
       </c>
       <c r="U16" t="n">
-        <v>0.764</v>
+        <v>0.5585</v>
       </c>
       <c r="V16" t="n">
         <v>-1.1675</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.329</v>
+        <v>-0.2116</v>
       </c>
       <c r="E17" t="n">
         <v>-0.3115</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0175</v>
+        <v>0.0999</v>
       </c>
       <c r="G17" t="n">
         <v>1.4347</v>
@@ -1780,13 +1780,13 @@
         <v>0.2081</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4932</v>
+        <v>-0.3758</v>
       </c>
       <c r="T17" t="n">
         <v>-0.3262</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.167</v>
+        <v>-0.0496</v>
       </c>
       <c r="V17" t="n">
         <v>-0.23</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. BIRD-JELINEK</t>
+          <t>A. INFANTE GUTIERREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2599</v>
+        <v>-1.6211</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0223</v>
+        <v>-0.6552</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2822</v>
+        <v>-0.9659</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7624</v>
+        <v>-1.1741</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4881</v>
+        <v>-1.6909</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2743</v>
+        <v>0.5168</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6748</v>
+        <v>1.2183</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0959</v>
+        <v>-0.8619</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5788</v>
+        <v>2.0802</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.4372</v>
+        <v>-2.3924</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5841</v>
+        <v>-0.829</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8532</v>
+        <v>-1.5634</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8325</v>
+        <v>2.2893</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1</v>
+        <v>-0.5281</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6524</v>
+        <v>-0.8329</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4475</v>
+        <v>0.3047</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.23</v>
+        <v>-1.1675</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.23</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. INFANTE GUTIERREZ</t>
+          <t>A. BIRD-JELINEK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5243</v>
+        <v>-2.1718</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2981</v>
+        <v>0.0223</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2262</v>
+        <v>-2.1942</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1741</v>
+        <v>-1.7624</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6909</v>
+        <v>-1.4881</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5168</v>
+        <v>-0.2743</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2183</v>
+        <v>0.6748</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8619</v>
+        <v>0.0959</v>
       </c>
       <c r="L19" t="n">
-        <v>2.0802</v>
+        <v>0.5788</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3924</v>
+        <v>-2.4372</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.829</v>
+        <v>-1.5841</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.5634</v>
+        <v>-0.8532</v>
       </c>
       <c r="P19" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2893</v>
+        <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4314</v>
+        <v>-1.0119</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.4758</v>
+        <v>-0.6524</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0444</v>
+        <v>-0.3595</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.9208</v>
+        <v>-5.3533</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.0886</v>
+        <v>-4.5172</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8322000000000001</v>
+        <v>-0.8361</v>
       </c>
       <c r="G20" t="n">
         <v>-3.9036</v>
@@ -2014,13 +2014,13 @@
         <v>1.4568</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1879</v>
+        <v>-0.2447</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0586</v>
+        <v>-0.37</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1292</v>
+        <v>0.1253</v>
       </c>
       <c r="V20" t="n">
         <v>0.4599</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.1932</v>
+        <v>-5.5925</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0007</v>
+        <v>-3.4293</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1925</v>
+        <v>-2.1632</v>
       </c>
       <c r="G21" t="n">
         <v>-6.5329</v>
@@ -2092,13 +2092,13 @@
         <v>2.0812</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2772</v>
+        <v>-0.122</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1487</v>
+        <v>-0.28</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1286</v>
+        <v>0.1579</v>
       </c>
       <c r="V21" t="n">
         <v>0.23</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.696100000000002</v>
+        <v>-3.9818</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4271</v>
+        <v>-2.426999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.268899999999999</v>
+        <v>-1.5547</v>
       </c>
       <c r="G22" t="n">
         <v>-2.347599999999999</v>
@@ -2170,13 +2170,13 @@
         <v>12.4872</v>
       </c>
       <c r="S22" t="n">
-        <v>-3.5099</v>
+        <v>-2.7956</v>
       </c>
       <c r="T22" t="n">
-        <v>-4.7237</v>
+        <v>-4.723800000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>1.2139</v>
+        <v>1.9281</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9198999999999999</v>
